--- a/simulation_study/copula_mis_spec/experiment_results.xlsx
+++ b/simulation_study/copula_mis_spec/experiment_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eric/Desktop/revised_version_20251208/Local dependence toolbox 20251208/simulation_study/copula_mis_spec/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eric/Desktop/revised_version_20250306/local dependence toolbox/simulation_study/copula_mis_spec/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44644671-4E27-3C46-8177-4E85B4329A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B371807D-2C5B-B34C-9059-1CDC06CC00F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5660" yWindow="500" windowWidth="20780" windowHeight="15920" xr2:uid="{772B97B5-03B2-AC48-B62B-9B7792D58D6B}"/>
   </bookViews>
@@ -338,15 +338,6 @@
     <xf numFmtId="183" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="183" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -389,6 +380,15 @@
     <xf numFmtId="182" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -412,9 +412,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -452,7 +452,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -558,7 +558,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -700,7 +700,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -730,59 +730,59 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1"/>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="41" t="s">
+      <c r="C1" s="53"/>
+      <c r="D1" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="40" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="41" t="s">
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
     </row>
     <row r="2" spans="1:18">
       <c r="A2"/>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="41" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="40" t="s">
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="41" t="s">
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
@@ -877,7 +877,7 @@
       <c r="L4" s="13">
         <v>1.3824208122956001E-2</v>
       </c>
-      <c r="M4" s="42">
+      <c r="M4" s="39">
         <v>0</v>
       </c>
       <c r="N4" s="35">
@@ -892,7 +892,7 @@
       <c r="Q4" s="35">
         <v>3.3268760854410001E-3</v>
       </c>
-      <c r="R4" s="42">
+      <c r="R4" s="39">
         <v>0</v>
       </c>
     </row>
@@ -927,7 +927,7 @@
       <c r="L5" s="13">
         <v>6.0647394189819997E-3</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="39">
         <v>0</v>
       </c>
       <c r="N5" s="35">
@@ -942,7 +942,7 @@
       <c r="Q5" s="35">
         <v>1.427745086087E-3</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="39">
         <v>0</v>
       </c>
     </row>
@@ -977,7 +977,7 @@
       <c r="L6" s="13">
         <v>4.2990551554980003E-3</v>
       </c>
-      <c r="M6" s="42">
+      <c r="M6" s="39">
         <v>0</v>
       </c>
       <c r="N6" s="35">
@@ -992,7 +992,7 @@
       <c r="Q6" s="35">
         <v>1.0091417500159999E-3</v>
       </c>
-      <c r="R6" s="42">
+      <c r="R6" s="39">
         <v>0</v>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       <c r="L7" s="15">
         <v>1.9597463166158999E-2</v>
       </c>
-      <c r="M7" s="43">
+      <c r="M7" s="40">
         <v>0</v>
       </c>
       <c r="N7" s="36">
@@ -1045,7 +1045,7 @@
       <c r="Q7" s="36">
         <v>5.5174962720440004E-3</v>
       </c>
-      <c r="R7" s="45">
+      <c r="R7" s="42">
         <v>0</v>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       <c r="L8" s="15">
         <v>8.6586750517600002E-3</v>
       </c>
-      <c r="M8" s="43">
+      <c r="M8" s="40">
         <v>0</v>
       </c>
       <c r="N8" s="36">
@@ -1096,7 +1096,7 @@
       <c r="Q8" s="36">
         <v>2.395807055547E-3</v>
       </c>
-      <c r="R8" s="45">
+      <c r="R8" s="42">
         <v>0</v>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       <c r="L9" s="15">
         <v>6.1142850854500001E-3</v>
       </c>
-      <c r="M9" s="43">
+      <c r="M9" s="40">
         <v>0</v>
       </c>
       <c r="N9" s="36">
@@ -1147,7 +1147,7 @@
       <c r="Q9" s="36">
         <v>1.6842599625100001E-3</v>
       </c>
-      <c r="R9" s="45">
+      <c r="R9" s="42">
         <v>0</v>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       <c r="L10" s="13">
         <v>2.9321222338283999E-2</v>
       </c>
-      <c r="M10" s="42">
+      <c r="M10" s="39">
         <v>0</v>
       </c>
       <c r="N10" s="35">
@@ -1200,7 +1200,7 @@
       <c r="Q10" s="35">
         <v>1.0183411163352999E-2</v>
       </c>
-      <c r="R10" s="42">
+      <c r="R10" s="39">
         <v>0</v>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       <c r="L11" s="13">
         <v>1.3113518953578001E-2</v>
       </c>
-      <c r="M11" s="42">
+      <c r="M11" s="39">
         <v>0</v>
       </c>
       <c r="N11" s="35">
@@ -1251,7 +1251,7 @@
       <c r="Q11" s="35">
         <v>1.3113518953578001E-2</v>
       </c>
-      <c r="R11" s="42">
+      <c r="R11" s="39">
         <v>0</v>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       <c r="L12" s="13">
         <v>9.2591611353130005E-3</v>
       </c>
-      <c r="M12" s="42">
+      <c r="M12" s="39">
         <v>0</v>
       </c>
       <c r="N12" s="35">
@@ -1302,7 +1302,7 @@
       <c r="Q12" s="35">
         <v>3.1041877928640002E-3</v>
       </c>
-      <c r="R12" s="42">
+      <c r="R12" s="39">
         <v>0</v>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       <c r="L13" s="16">
         <v>1.7846541775706999E-2</v>
       </c>
-      <c r="M13" s="44">
+      <c r="M13" s="41">
         <v>0</v>
       </c>
       <c r="N13" s="36">
@@ -1358,7 +1358,7 @@
       <c r="Q13" s="36">
         <v>9.670535204393E-3</v>
       </c>
-      <c r="R13" s="45">
+      <c r="R13" s="42">
         <v>0</v>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       <c r="L14" s="16">
         <v>7.8545827985929996E-3</v>
       </c>
-      <c r="M14" s="44">
+      <c r="M14" s="41">
         <v>0</v>
       </c>
       <c r="N14" s="36">
@@ -1409,7 +1409,7 @@
       <c r="Q14" s="36">
         <v>4.191188928421E-3</v>
       </c>
-      <c r="R14" s="45">
+      <c r="R14" s="42">
         <v>0</v>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       <c r="L15" s="16">
         <v>5.542201794529E-3</v>
       </c>
-      <c r="M15" s="44">
+      <c r="M15" s="41">
         <v>0</v>
       </c>
       <c r="N15" s="36">
@@ -1460,7 +1460,7 @@
       <c r="Q15" s="36">
         <v>2.9501946761610002E-3</v>
       </c>
-      <c r="R15" s="45">
+      <c r="R15" s="42">
         <v>0</v>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       <c r="L16" s="13">
         <v>2.441980246034E-2</v>
       </c>
-      <c r="M16" s="42">
+      <c r="M16" s="39">
         <v>0</v>
       </c>
       <c r="N16" s="35">
@@ -1513,7 +1513,7 @@
       <c r="Q16" s="35">
         <v>1.4294502872575001E-2</v>
       </c>
-      <c r="R16" s="42">
+      <c r="R16" s="39">
         <v>0</v>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       <c r="L17" s="13">
         <v>1.0891119995030001E-2</v>
       </c>
-      <c r="M17" s="42">
+      <c r="M17" s="39">
         <v>0</v>
       </c>
       <c r="N17" s="35">
@@ -1563,7 +1563,7 @@
       <c r="Q17" s="35">
         <v>6.2885982972069997E-3</v>
       </c>
-      <c r="R17" s="42">
+      <c r="R17" s="39">
         <v>0</v>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       <c r="L18" s="13">
         <v>7.6907412265400004E-3</v>
       </c>
-      <c r="M18" s="42">
+      <c r="M18" s="39">
         <v>0</v>
       </c>
       <c r="N18" s="35">
@@ -1613,7 +1613,7 @@
       <c r="Q18" s="35">
         <v>4.436141939288E-3</v>
       </c>
-      <c r="R18" s="42">
+      <c r="R18" s="39">
         <v>0</v>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       <c r="L19" s="16">
         <v>3.4842527819595001E-2</v>
       </c>
-      <c r="M19" s="44">
+      <c r="M19" s="41">
         <v>0</v>
       </c>
       <c r="N19" s="36">
@@ -1666,7 +1666,7 @@
       <c r="Q19" s="36">
         <v>2.2799903373389999E-2</v>
       </c>
-      <c r="R19" s="45">
+      <c r="R19" s="42">
         <v>0</v>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       <c r="L20" s="16">
         <v>1.5856126644993002E-2</v>
       </c>
-      <c r="M20" s="44">
+      <c r="M20" s="41">
         <v>0</v>
       </c>
       <c r="N20" s="36">
@@ -1717,7 +1717,7 @@
       <c r="Q20" s="36">
         <v>1.0634960515392001E-2</v>
       </c>
-      <c r="R20" s="45">
+      <c r="R20" s="42">
         <v>0</v>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       <c r="L21" s="16">
         <v>1.1194698220686E-2</v>
       </c>
-      <c r="M21" s="44">
+      <c r="M21" s="41">
         <v>0</v>
       </c>
       <c r="N21" s="36">
@@ -1768,7 +1768,7 @@
       <c r="Q21" s="36">
         <v>7.171329183888E-3</v>
       </c>
-      <c r="R21" s="45">
+      <c r="R21" s="42">
         <v>0</v>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       <c r="L22" s="13">
         <v>3.8210193858889997E-2</v>
       </c>
-      <c r="M22" s="42">
+      <c r="M22" s="39">
         <v>0</v>
       </c>
       <c r="N22" s="35">
@@ -1859,7 +1859,7 @@
       <c r="L23" s="13">
         <v>1.5796657143121999E-2</v>
       </c>
-      <c r="M23" s="42">
+      <c r="M23" s="39">
         <v>0</v>
       </c>
       <c r="N23" s="35">
@@ -1874,7 +1874,7 @@
       <c r="Q23" s="35">
         <v>1.426158215597E-3</v>
       </c>
-      <c r="R23" s="42">
+      <c r="R23" s="39">
         <v>0</v>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       <c r="L24" s="13">
         <v>1.110837617357E-2</v>
       </c>
-      <c r="M24" s="42">
+      <c r="M24" s="39">
         <v>0</v>
       </c>
       <c r="N24" s="35">
@@ -1924,7 +1924,7 @@
       <c r="Q24" s="35">
         <v>1.0089831043719999E-3</v>
       </c>
-      <c r="R24" s="42">
+      <c r="R24" s="39">
         <v>0</v>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       <c r="L25" s="16">
         <v>3.6180454013659998E-2</v>
       </c>
-      <c r="M25" s="44">
+      <c r="M25" s="41">
         <v>0</v>
       </c>
       <c r="N25" s="36">
@@ -1977,7 +1977,7 @@
       <c r="Q25" s="36">
         <v>5.5056921418790003E-3</v>
       </c>
-      <c r="R25" s="45">
+      <c r="R25" s="42">
         <v>0</v>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       <c r="L26" s="16">
         <v>1.6341269304018E-2</v>
       </c>
-      <c r="M26" s="44">
+      <c r="M26" s="41">
         <v>0</v>
       </c>
       <c r="N26" s="36">
@@ -2028,7 +2028,7 @@
       <c r="Q26" s="36">
         <v>2.3759589851660001E-3</v>
       </c>
-      <c r="R26" s="45">
+      <c r="R26" s="42">
         <v>0</v>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       <c r="L27" s="16">
         <v>1.1597049460642999E-2</v>
       </c>
-      <c r="M27" s="44">
+      <c r="M27" s="41">
         <v>0</v>
       </c>
       <c r="N27" s="36">
@@ -2079,7 +2079,7 @@
       <c r="Q27" s="36">
         <v>1.6832188588540001E-3</v>
       </c>
-      <c r="R27" s="45">
+      <c r="R27" s="42">
         <v>0</v>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       <c r="L28" s="13">
         <v>3.9911557601228997E-2</v>
       </c>
-      <c r="M28" s="42">
+      <c r="M28" s="39">
         <v>0</v>
       </c>
       <c r="N28" s="35">
@@ -2132,7 +2132,7 @@
       <c r="Q28" s="35">
         <v>1.0142639743210001E-2</v>
       </c>
-      <c r="R28" s="42">
+      <c r="R28" s="39">
         <v>0</v>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       <c r="L29" s="13">
         <v>1.8410187290969E-2</v>
       </c>
-      <c r="M29" s="42">
+      <c r="M29" s="39">
         <v>0</v>
       </c>
       <c r="N29" s="35">
@@ -2183,7 +2183,7 @@
       <c r="Q29" s="35">
         <v>4.8150670735509996E-3</v>
       </c>
-      <c r="R29" s="42">
+      <c r="R29" s="39">
         <v>0</v>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       <c r="L30" s="13">
         <v>1.3108684421574E-2</v>
       </c>
-      <c r="M30" s="42">
+      <c r="M30" s="39">
         <v>0</v>
       </c>
       <c r="N30" s="35">
@@ -2234,7 +2234,7 @@
       <c r="Q30" s="35">
         <v>3.0981620219290001E-3</v>
       </c>
-      <c r="R30" s="42">
+      <c r="R30" s="39">
         <v>0</v>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       <c r="L32" s="16">
         <v>1.7871773828527001E-2</v>
       </c>
-      <c r="M32" s="44">
+      <c r="M32" s="41">
         <v>0</v>
       </c>
       <c r="N32" s="36">
@@ -2341,7 +2341,7 @@
       <c r="Q32" s="36">
         <v>4.1808713111489999E-3</v>
       </c>
-      <c r="R32" s="45">
+      <c r="R32" s="42">
         <v>0</v>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       <c r="L33" s="16">
         <v>1.2586263984115E-2</v>
       </c>
-      <c r="M33" s="44">
+      <c r="M33" s="41">
         <v>0</v>
       </c>
       <c r="N33" s="36">
@@ -2392,7 +2392,7 @@
       <c r="Q33" s="36">
         <v>2.9634701101330001E-3</v>
       </c>
-      <c r="R33" s="45">
+      <c r="R33" s="42">
         <v>0</v>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       <c r="L34" s="13">
         <v>3.9068075608137E-2</v>
       </c>
-      <c r="M34" s="42">
+      <c r="M34" s="39">
         <v>0</v>
       </c>
       <c r="N34" s="35">
@@ -2480,7 +2480,7 @@
       <c r="L35" s="13">
         <v>1.7543620397511998E-2</v>
       </c>
-      <c r="M35" s="42">
+      <c r="M35" s="39">
         <v>0</v>
       </c>
       <c r="N35" s="35">
@@ -2495,7 +2495,7 @@
       <c r="Q35" s="35">
         <v>6.2861700103360001E-3</v>
       </c>
-      <c r="R35" s="42">
+      <c r="R35" s="39">
         <v>0</v>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       <c r="L36" s="13">
         <v>1.2309281782198001E-2</v>
       </c>
-      <c r="M36" s="42">
+      <c r="M36" s="39">
         <v>0</v>
       </c>
       <c r="N36" s="35">
@@ -2545,7 +2545,7 @@
       <c r="Q36" s="35">
         <v>4.4288878162490001E-3</v>
       </c>
-      <c r="R36" s="42">
+      <c r="R36" s="39">
         <v>0</v>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       <c r="L37" s="16">
         <v>4.1596319787162002E-2</v>
       </c>
-      <c r="M37" s="44">
+      <c r="M37" s="41">
         <v>0</v>
       </c>
       <c r="N37" s="36">
@@ -2598,7 +2598,7 @@
       <c r="Q37" s="36">
         <v>2.2895524352097001E-2</v>
       </c>
-      <c r="R37" s="45">
+      <c r="R37" s="42">
         <v>0</v>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       <c r="L38" s="16">
         <v>1.9066662131617999E-2</v>
       </c>
-      <c r="M38" s="44">
+      <c r="M38" s="41">
         <v>0</v>
       </c>
       <c r="N38" s="36">
@@ -2649,7 +2649,7 @@
       <c r="Q38" s="36">
         <v>1.0726857632912999E-2</v>
       </c>
-      <c r="R38" s="45">
+      <c r="R38" s="42">
         <v>0</v>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       <c r="L39" s="16">
         <v>1.3491782008159999E-2</v>
       </c>
-      <c r="M39" s="44">
+      <c r="M39" s="41">
         <v>0</v>
       </c>
       <c r="N39" s="36">
@@ -2700,7 +2700,7 @@
       <c r="Q39" s="36">
         <v>7.1357569687379996E-3</v>
       </c>
-      <c r="R39" s="45">
+      <c r="R39" s="42">
         <v>0</v>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       <c r="L47" s="13">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="M47" s="42">
+      <c r="M47" s="39">
         <v>0</v>
       </c>
       <c r="N47" s="35">
@@ -3151,7 +3151,7 @@
       <c r="L48" s="13">
         <v>8.8946000000000001E-4</v>
       </c>
-      <c r="M48" s="42">
+      <c r="M48" s="39">
         <v>0</v>
       </c>
       <c r="N48" s="35">
@@ -3462,7 +3462,7 @@
       <c r="L54" s="13">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="M54" s="42">
+      <c r="M54" s="39">
         <v>1E-3</v>
       </c>
       <c r="N54" s="35">
@@ -3566,7 +3566,7 @@
       <c r="L56" s="16">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="M56" s="44">
+      <c r="M56" s="41">
         <v>0</v>
       </c>
       <c r="N56" s="36">
@@ -3617,7 +3617,7 @@
       <c r="L57" s="16">
         <v>3.3E-3</v>
       </c>
-      <c r="M57" s="44">
+      <c r="M57" s="41">
         <v>0</v>
       </c>
       <c r="N57" s="36">
@@ -3679,59 +3679,59 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1"/>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="41" t="s">
+      <c r="C1" s="53"/>
+      <c r="D1" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="39" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="41" t="s">
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
     </row>
     <row r="2" spans="1:18">
       <c r="A2"/>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="41" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="39" t="s">
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="41" t="s">
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
@@ -3841,7 +3841,7 @@
       <c r="Q4" s="26">
         <v>2.333686180778E-3</v>
       </c>
-      <c r="R4" s="46">
+      <c r="R4" s="43">
         <v>0</v>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       <c r="Q5" s="26">
         <v>1.029588821005E-3</v>
       </c>
-      <c r="R5" s="46">
+      <c r="R5" s="43">
         <v>0</v>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       <c r="L6" s="7">
         <v>1.8311446631822E-2</v>
       </c>
-      <c r="M6" s="48">
+      <c r="M6" s="45">
         <v>0</v>
       </c>
       <c r="N6" s="26">
@@ -3941,7 +3941,7 @@
       <c r="Q6" s="26">
         <v>7.2289131682867595E-4</v>
       </c>
-      <c r="R6" s="46">
+      <c r="R6" s="43">
         <v>0</v>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       <c r="Q7" s="28">
         <v>5.555603614416E-3</v>
       </c>
-      <c r="R7" s="47">
+      <c r="R7" s="44">
         <v>0</v>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       <c r="L8" s="12">
         <v>2.3975582340171001E-2</v>
       </c>
-      <c r="M8" s="49">
+      <c r="M8" s="46">
         <v>0</v>
       </c>
       <c r="N8" s="28">
@@ -4045,7 +4045,7 @@
       <c r="Q8" s="28">
         <v>2.4072403548110002E-3</v>
       </c>
-      <c r="R8" s="47">
+      <c r="R8" s="44">
         <v>0</v>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       <c r="L9" s="12">
         <v>1.6976603405177999E-2</v>
       </c>
-      <c r="M9" s="49">
+      <c r="M9" s="46">
         <v>0</v>
       </c>
       <c r="N9" s="28">
@@ -4096,7 +4096,7 @@
       <c r="Q9" s="28">
         <v>1.6934985429909999E-3</v>
       </c>
-      <c r="R9" s="47">
+      <c r="R9" s="44">
         <v>0</v>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       <c r="Q10" s="26">
         <v>9.9167624289459994E-3</v>
       </c>
-      <c r="R10" s="46">
+      <c r="R10" s="43">
         <v>0</v>
       </c>
     </row>
@@ -4185,7 +4185,7 @@
       <c r="L11" s="7">
         <v>2.2137385284191E-2</v>
       </c>
-      <c r="M11" s="48">
+      <c r="M11" s="45">
         <v>0</v>
       </c>
       <c r="N11" s="26">
@@ -4200,7 +4200,7 @@
       <c r="Q11" s="26">
         <v>4.9115074107499998E-3</v>
       </c>
-      <c r="R11" s="46">
+      <c r="R11" s="43">
         <v>0</v>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       <c r="L12" s="7">
         <v>1.5587924367596999E-2</v>
       </c>
-      <c r="M12" s="48">
+      <c r="M12" s="45">
         <v>0</v>
       </c>
       <c r="N12" s="26">
@@ -4251,7 +4251,7 @@
       <c r="Q12" s="26">
         <v>3.0399374120859998E-3</v>
       </c>
-      <c r="R12" s="46">
+      <c r="R12" s="43">
         <v>0</v>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       <c r="Q14" s="28">
         <v>3.2153642437699999E-3</v>
       </c>
-      <c r="R14" s="47">
+      <c r="R14" s="44">
         <v>0</v>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       <c r="L15" s="12">
         <v>1.8208043362337001E-2</v>
       </c>
-      <c r="M15" s="49">
+      <c r="M15" s="46">
         <v>0</v>
       </c>
       <c r="N15" s="28">
@@ -4409,7 +4409,7 @@
       <c r="Q15" s="28">
         <v>2.2704573378240001E-3</v>
       </c>
-      <c r="R15" s="47">
+      <c r="R15" s="44">
         <v>0</v>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       <c r="L17" s="7">
         <v>2.3935389072675999E-2</v>
       </c>
-      <c r="M17" s="48">
+      <c r="M17" s="45">
         <v>0</v>
       </c>
       <c r="N17" s="26">
@@ -4512,7 +4512,7 @@
       <c r="Q17" s="26">
         <v>6.3242897319699997E-3</v>
       </c>
-      <c r="R17" s="46">
+      <c r="R17" s="43">
         <v>0</v>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       <c r="L18" s="7">
         <v>1.6999109080762999E-2</v>
       </c>
-      <c r="M18" s="48">
+      <c r="M18" s="45">
         <v>0</v>
       </c>
       <c r="N18" s="26">
@@ -4562,7 +4562,7 @@
       <c r="Q18" s="26">
         <v>4.4396438344450001E-3</v>
       </c>
-      <c r="R18" s="46">
+      <c r="R18" s="43">
         <v>0</v>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       <c r="L20" s="12">
         <v>2.2004096198325E-2</v>
       </c>
-      <c r="M20" s="49">
+      <c r="M20" s="46">
         <v>0</v>
       </c>
       <c r="N20" s="28">
@@ -4702,7 +4702,7 @@
       <c r="L21" s="12">
         <v>1.5655570294641999E-2</v>
       </c>
-      <c r="M21" s="49">
+      <c r="M21" s="46">
         <v>0</v>
       </c>
       <c r="N21" s="28">
@@ -4717,7 +4717,7 @@
       <c r="Q21" s="28">
         <v>6.91986048454E-3</v>
       </c>
-      <c r="R21" s="47">
+      <c r="R21" s="44">
         <v>0</v>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       <c r="L22" s="7">
         <v>2.6417374596095401E-4</v>
       </c>
-      <c r="M22" s="48">
+      <c r="M22" s="45">
         <v>0</v>
       </c>
       <c r="N22" s="26">
@@ -4773,7 +4773,7 @@
       <c r="Q22" s="26">
         <v>2.3943180197510002E-3</v>
       </c>
-      <c r="R22" s="46">
+      <c r="R22" s="43">
         <v>0</v>
       </c>
     </row>
@@ -4808,7 +4808,7 @@
       <c r="L23" s="7">
         <v>1.01588273736406E-4</v>
       </c>
-      <c r="M23" s="48">
+      <c r="M23" s="45">
         <v>0</v>
       </c>
       <c r="N23" s="26">
@@ -4823,7 +4823,7 @@
       <c r="Q23" s="26">
         <v>1.0247582937420001E-3</v>
       </c>
-      <c r="R23" s="46">
+      <c r="R23" s="43">
         <v>0</v>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       <c r="L24" s="7">
         <v>7.0532096197607397E-5</v>
       </c>
-      <c r="M24" s="48">
+      <c r="M24" s="45">
         <v>0</v>
       </c>
       <c r="N24" s="26">
@@ -4873,7 +4873,7 @@
       <c r="Q24" s="26">
         <v>7.2072658783358203E-4</v>
       </c>
-      <c r="R24" s="46">
+      <c r="R24" s="43">
         <v>0</v>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       <c r="L25" s="12">
         <v>7.7186686802827302E-4</v>
       </c>
-      <c r="M25" s="49">
+      <c r="M25" s="46">
         <v>0</v>
       </c>
       <c r="N25" s="28">
@@ -4926,7 +4926,7 @@
       <c r="Q25" s="28">
         <v>5.5411163147030002E-3</v>
       </c>
-      <c r="R25" s="47">
+      <c r="R25" s="44">
         <v>0</v>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       <c r="L26" s="12">
         <v>3.1408241890039601E-4</v>
       </c>
-      <c r="M26" s="49">
+      <c r="M26" s="46">
         <v>0</v>
       </c>
       <c r="N26" s="28">
@@ -4977,7 +4977,7 @@
       <c r="Q26" s="28">
         <v>2.399078172058E-3</v>
       </c>
-      <c r="R26" s="47">
+      <c r="R26" s="44">
         <v>0</v>
       </c>
     </row>
@@ -5013,7 +5013,7 @@
       <c r="L27" s="12">
         <v>2.18348099455732E-4</v>
       </c>
-      <c r="M27" s="49">
+      <c r="M27" s="46">
         <v>0</v>
       </c>
       <c r="N27" s="28">
@@ -5028,7 +5028,7 @@
       <c r="Q27" s="28">
         <v>1.695044991823E-3</v>
       </c>
-      <c r="R27" s="47">
+      <c r="R27" s="44">
         <v>0</v>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       <c r="L28" s="7">
         <v>1.7667471020819999E-3</v>
       </c>
-      <c r="M28" s="48">
+      <c r="M28" s="45">
         <v>0</v>
       </c>
       <c r="N28" s="26">
@@ -5081,7 +5081,7 @@
       <c r="Q28" s="26">
         <v>9.9374031910450002E-3</v>
       </c>
-      <c r="R28" s="46">
+      <c r="R28" s="43">
         <v>0</v>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       <c r="L29" s="7">
         <v>7.3418452452420296E-4</v>
       </c>
-      <c r="M29" s="48">
+      <c r="M29" s="45">
         <v>0</v>
       </c>
       <c r="N29" s="26">
@@ -5132,7 +5132,7 @@
       <c r="Q29" s="26">
         <v>4.75182653555E-3</v>
       </c>
-      <c r="R29" s="46">
+      <c r="R29" s="43">
         <v>0</v>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       <c r="L30" s="7">
         <v>5.0858670934756398E-4</v>
       </c>
-      <c r="M30" s="48">
+      <c r="M30" s="45">
         <v>0</v>
       </c>
       <c r="N30" s="26">
@@ -5183,7 +5183,7 @@
       <c r="Q30" s="26">
         <v>3.0164521201960001E-3</v>
       </c>
-      <c r="R30" s="46">
+      <c r="R30" s="43">
         <v>0</v>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       <c r="L31" s="12">
         <v>1.066005724726E-3</v>
       </c>
-      <c r="M31" s="49">
+      <c r="M31" s="46">
         <v>0</v>
       </c>
       <c r="N31" s="28">
@@ -5239,7 +5239,7 @@
       <c r="Q31" s="28">
         <v>7.4088110549960003E-3</v>
       </c>
-      <c r="R31" s="47">
+      <c r="R31" s="44">
         <v>0</v>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       <c r="L32" s="12">
         <v>4.2292489050317302E-4</v>
       </c>
-      <c r="M32" s="49">
+      <c r="M32" s="46">
         <v>0</v>
       </c>
       <c r="N32" s="28">
@@ -5290,7 +5290,7 @@
       <c r="Q32" s="28">
         <v>3.2206982343950001E-3</v>
       </c>
-      <c r="R32" s="47">
+      <c r="R32" s="44">
         <v>0</v>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       <c r="L33" s="12">
         <v>2.9217427532281898E-4</v>
       </c>
-      <c r="M33" s="49">
+      <c r="M33" s="46">
         <v>0</v>
       </c>
       <c r="N33" s="28">
@@ -5341,7 +5341,7 @@
       <c r="Q33" s="28">
         <v>2.2595385411729998E-3</v>
       </c>
-      <c r="R33" s="47">
+      <c r="R33" s="44">
         <v>0</v>
       </c>
     </row>
@@ -5379,7 +5379,7 @@
       <c r="L34" s="7">
         <v>2.8563294215380002E-3</v>
       </c>
-      <c r="M34" s="48">
+      <c r="M34" s="45">
         <v>0</v>
       </c>
       <c r="N34" s="26">
@@ -5394,7 +5394,7 @@
       <c r="Q34" s="26">
         <v>1.4446079386792999E-2</v>
       </c>
-      <c r="R34" s="46">
+      <c r="R34" s="43">
         <v>0</v>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       <c r="L35" s="7">
         <v>1.1872663752400001E-3</v>
       </c>
-      <c r="M35" s="48">
+      <c r="M35" s="45">
         <v>0</v>
       </c>
       <c r="N35" s="26">
@@ -5444,7 +5444,7 @@
       <c r="Q35" s="26">
         <v>6.3236190245339998E-3</v>
       </c>
-      <c r="R35" s="46">
+      <c r="R35" s="43">
         <v>0</v>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       <c r="L36" s="7">
         <v>8.2654461928373803E-4</v>
       </c>
-      <c r="M36" s="48">
+      <c r="M36" s="45">
         <v>0</v>
       </c>
       <c r="N36" s="26">
@@ -5494,7 +5494,7 @@
       <c r="Q36" s="26">
         <v>4.4555068365239999E-3</v>
       </c>
-      <c r="R36" s="46">
+      <c r="R36" s="43">
         <v>0</v>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       <c r="L37" s="12">
         <v>6.0271678288930002E-3</v>
       </c>
-      <c r="M37" s="49">
+      <c r="M37" s="46">
         <v>0</v>
       </c>
       <c r="N37" s="28">
@@ -5547,7 +5547,7 @@
       <c r="Q37" s="28">
         <v>2.2092441565216999E-2</v>
       </c>
-      <c r="R37" s="47">
+      <c r="R37" s="44">
         <v>0</v>
       </c>
     </row>
@@ -5583,7 +5583,7 @@
       <c r="L38" s="12">
         <v>2.5433683022589998E-3</v>
       </c>
-      <c r="M38" s="49">
+      <c r="M38" s="46">
         <v>0</v>
       </c>
       <c r="N38" s="28">
@@ -5598,7 +5598,7 @@
       <c r="Q38" s="28">
         <v>1.0515209943194E-2</v>
       </c>
-      <c r="R38" s="47">
+      <c r="R38" s="44">
         <v>0</v>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       <c r="L39" s="12">
         <v>1.7732038971510001E-3</v>
       </c>
-      <c r="M39" s="49">
+      <c r="M39" s="46">
         <v>0</v>
       </c>
       <c r="N39" s="28">
@@ -5649,7 +5649,7 @@
       <c r="Q39" s="28">
         <v>6.9238119554249997E-3</v>
       </c>
-      <c r="R39" s="47">
+      <c r="R39" s="44">
         <v>0</v>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       <c r="L42" s="7">
         <v>1.4231000000000001E-4</v>
       </c>
-      <c r="M42" s="48">
+      <c r="M42" s="45">
         <v>0</v>
       </c>
       <c r="N42" s="26">
@@ -5894,7 +5894,7 @@
       <c r="L44" s="12">
         <v>4.1115999999999999E-4</v>
       </c>
-      <c r="M44" s="49">
+      <c r="M44" s="46">
         <v>0</v>
       </c>
       <c r="N44" s="28">
@@ -5945,7 +5945,7 @@
       <c r="L45" s="12">
         <v>2.8992999999999998E-4</v>
       </c>
-      <c r="M45" s="49">
+      <c r="M45" s="46">
         <v>0</v>
       </c>
       <c r="N45" s="28">
@@ -6049,7 +6049,7 @@
       <c r="L47" s="7">
         <v>8.8999000000000001E-4</v>
       </c>
-      <c r="M47" s="48">
+      <c r="M47" s="45">
         <v>0</v>
       </c>
       <c r="N47" s="26">
@@ -6100,7 +6100,7 @@
       <c r="L48" s="7">
         <v>6.2286999999999998E-4</v>
       </c>
-      <c r="M48" s="48">
+      <c r="M48" s="45">
         <v>0</v>
       </c>
       <c r="N48" s="26">
@@ -6115,7 +6115,7 @@
       <c r="Q48" s="26">
         <v>1.8E-3</v>
       </c>
-      <c r="R48" s="46">
+      <c r="R48" s="43">
         <v>0</v>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       <c r="L51" s="12">
         <v>5.6996E-4</v>
       </c>
-      <c r="M51" s="49">
+      <c r="M51" s="46">
         <v>0</v>
       </c>
       <c r="N51" s="28">
@@ -6361,7 +6361,7 @@
       <c r="L53" s="7">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="M53" s="48">
+      <c r="M53" s="45">
         <v>0</v>
       </c>
       <c r="N53" s="26">
@@ -6411,7 +6411,7 @@
       <c r="L54" s="7">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="M54" s="48">
+      <c r="M54" s="45">
         <v>0</v>
       </c>
       <c r="N54" s="26">
@@ -6515,7 +6515,7 @@
       <c r="L56" s="12">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="M56" s="49">
+      <c r="M56" s="46">
         <v>0</v>
       </c>
       <c r="N56" s="28">
@@ -6566,7 +6566,7 @@
       <c r="L57" s="12">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="M57" s="49">
+      <c r="M57" s="46">
         <v>0</v>
       </c>
       <c r="N57" s="28">
@@ -6581,7 +6581,7 @@
       <c r="Q57" s="28">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="R57" s="47">
+      <c r="R57" s="44">
         <v>0</v>
       </c>
     </row>
@@ -6626,59 +6626,59 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1"/>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="41" t="s">
+      <c r="C1" s="53"/>
+      <c r="D1" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="39" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="41" t="s">
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
     </row>
     <row r="2" spans="1:18">
       <c r="A2"/>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="41" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="39" t="s">
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="41" t="s">
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
@@ -6977,7 +6977,7 @@
       <c r="L8" s="12">
         <v>6.1775694951390001E-3</v>
       </c>
-      <c r="M8" s="50">
+      <c r="M8" s="47">
         <v>0</v>
       </c>
       <c r="N8" s="28">
@@ -6992,7 +6992,7 @@
       <c r="Q8" s="28">
         <v>2.4879571239357998E-2</v>
       </c>
-      <c r="R8" s="55">
+      <c r="R8" s="52">
         <v>0</v>
       </c>
     </row>
@@ -7028,7 +7028,7 @@
       <c r="L9" s="12">
         <v>4.344516810638E-3</v>
       </c>
-      <c r="M9" s="50">
+      <c r="M9" s="47">
         <v>0</v>
       </c>
       <c r="N9" s="28">
@@ -7043,7 +7043,7 @@
       <c r="Q9" s="28">
         <v>1.7767419118975E-2</v>
       </c>
-      <c r="R9" s="55">
+      <c r="R9" s="52">
         <v>0</v>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       <c r="Q10" s="26">
         <v>5.3392922707176001E-2</v>
       </c>
-      <c r="R10" s="51">
+      <c r="R10" s="48">
         <v>0</v>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       <c r="L11" s="7">
         <v>9.0065645792419997E-3</v>
       </c>
-      <c r="M11" s="51">
+      <c r="M11" s="48">
         <v>0</v>
       </c>
       <c r="N11" s="26">
@@ -7147,7 +7147,7 @@
       <c r="Q11" s="26">
         <v>2.5427199324344001E-2</v>
       </c>
-      <c r="R11" s="51">
+      <c r="R11" s="48">
         <v>0</v>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       <c r="L12" s="7">
         <v>6.3304335161220001E-3</v>
       </c>
-      <c r="M12" s="51">
+      <c r="M12" s="48">
         <v>0</v>
       </c>
       <c r="N12" s="26">
@@ -7198,7 +7198,7 @@
       <c r="Q12" s="26">
         <v>1.7970409180786E-2</v>
       </c>
-      <c r="R12" s="51">
+      <c r="R12" s="48">
         <v>0</v>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       <c r="Q17" s="26">
         <v>2.5040265659399999E-2</v>
       </c>
-      <c r="R17" s="51">
+      <c r="R17" s="48">
         <v>0</v>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
       <c r="L18" s="7">
         <v>5.5730090193059998E-3</v>
       </c>
-      <c r="M18" s="51">
+      <c r="M18" s="48">
         <v>0</v>
       </c>
       <c r="N18" s="26">
@@ -7509,7 +7509,7 @@
       <c r="Q18" s="26">
         <v>1.7706607740063999E-2</v>
       </c>
-      <c r="R18" s="51">
+      <c r="R18" s="48">
         <v>0</v>
       </c>
     </row>
@@ -7613,7 +7613,7 @@
       <c r="Q20" s="28">
         <v>2.5127151750777E-2</v>
       </c>
-      <c r="R20" s="55">
+      <c r="R20" s="52">
         <v>0</v>
       </c>
     </row>
@@ -7649,7 +7649,7 @@
       <c r="L21" s="12">
         <v>7.8396443205990003E-3</v>
       </c>
-      <c r="M21" s="50">
+      <c r="M21" s="47">
         <v>0</v>
       </c>
       <c r="N21" s="28">
@@ -7664,7 +7664,7 @@
       <c r="Q21" s="28">
         <v>1.7936508466537E-2</v>
       </c>
-      <c r="R21" s="55">
+      <c r="R21" s="52">
         <v>0</v>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       <c r="Q23" s="26">
         <v>5.8542285215597101E-5</v>
       </c>
-      <c r="R23" s="51">
+      <c r="R23" s="48">
         <v>0</v>
       </c>
     </row>
@@ -7820,7 +7820,7 @@
       <c r="Q24" s="26">
         <v>4.0915680014769799E-5</v>
       </c>
-      <c r="R24" s="51">
+      <c r="R24" s="48">
         <v>0</v>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       <c r="L25" s="12">
         <v>3.1487860619270003E-2</v>
       </c>
-      <c r="M25" s="50">
+      <c r="M25" s="47">
         <v>0</v>
       </c>
       <c r="N25" s="28">
@@ -7873,7 +7873,7 @@
       <c r="Q25" s="28">
         <v>5.1223137307615095E-4</v>
       </c>
-      <c r="R25" s="55">
+      <c r="R25" s="52">
         <v>0</v>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       <c r="L26" s="12">
         <v>1.4019520982179999E-2</v>
       </c>
-      <c r="M26" s="50">
+      <c r="M26" s="47">
         <v>0</v>
       </c>
       <c r="N26" s="28">
@@ -7924,7 +7924,7 @@
       <c r="Q26" s="28">
         <v>2.0582274329848299E-4</v>
       </c>
-      <c r="R26" s="55">
+      <c r="R26" s="52">
         <v>0</v>
       </c>
     </row>
@@ -7960,7 +7960,7 @@
       <c r="L27" s="12">
         <v>9.9009396682400008E-3</v>
       </c>
-      <c r="M27" s="50">
+      <c r="M27" s="47">
         <v>0</v>
       </c>
       <c r="N27" s="28">
@@ -7975,7 +7975,7 @@
       <c r="Q27" s="28">
         <v>1.4397639097559199E-4</v>
       </c>
-      <c r="R27" s="55">
+      <c r="R27" s="52">
         <v>0</v>
       </c>
     </row>
@@ -8013,7 +8013,7 @@
       <c r="L28" s="7">
         <v>3.2153852784098998E-2</v>
       </c>
-      <c r="M28" s="51">
+      <c r="M28" s="48">
         <v>0</v>
       </c>
       <c r="N28" s="26">
@@ -8028,7 +8028,7 @@
       <c r="Q28" s="26">
         <v>1.1038315563840001E-3</v>
       </c>
-      <c r="R28" s="51">
+      <c r="R28" s="48">
         <v>0</v>
       </c>
     </row>
@@ -8064,7 +8064,7 @@
       <c r="L29" s="7">
         <v>1.4733893500004E-2</v>
       </c>
-      <c r="M29" s="51">
+      <c r="M29" s="48">
         <v>0</v>
       </c>
       <c r="N29" s="26">
@@ -8079,7 +8079,7 @@
       <c r="Q29" s="26">
         <v>4.5325599473615099E-4</v>
       </c>
-      <c r="R29" s="51">
+      <c r="R29" s="48">
         <v>0</v>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       <c r="L30" s="7">
         <v>1.0489991077557E-2</v>
       </c>
-      <c r="M30" s="51">
+      <c r="M30" s="48">
         <v>0</v>
       </c>
       <c r="N30" s="26">
@@ -8130,7 +8130,7 @@
       <c r="Q30" s="26">
         <v>3.1607261577328E-4</v>
       </c>
-      <c r="R30" s="51">
+      <c r="R30" s="48">
         <v>0</v>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       <c r="Q32" s="28">
         <v>2.5471043054774801E-4</v>
       </c>
-      <c r="R32" s="55">
+      <c r="R32" s="52">
         <v>0</v>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       <c r="Q33" s="28">
         <v>1.78378847896677E-4</v>
       </c>
-      <c r="R33" s="55">
+      <c r="R33" s="52">
         <v>0</v>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       <c r="L34" s="7">
         <v>3.4663217125567997E-2</v>
       </c>
-      <c r="M34" s="51">
+      <c r="M34" s="48">
         <v>0</v>
       </c>
       <c r="N34" s="26">
@@ -8341,7 +8341,7 @@
       <c r="Q34" s="26">
         <v>1.9763859390509999E-3</v>
       </c>
-      <c r="R34" s="51">
+      <c r="R34" s="48">
         <v>0</v>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       <c r="L35" s="7">
         <v>1.5409423828358E-2</v>
       </c>
-      <c r="M35" s="51">
+      <c r="M35" s="48">
         <v>0</v>
       </c>
       <c r="N35" s="26">
@@ -8391,7 +8391,7 @@
       <c r="Q35" s="26">
         <v>8.1154800045272503E-4</v>
       </c>
-      <c r="R35" s="51">
+      <c r="R35" s="48">
         <v>0</v>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       <c r="L36" s="7">
         <v>1.0870476145754E-2</v>
       </c>
-      <c r="M36" s="51">
+      <c r="M36" s="48">
         <v>0</v>
       </c>
       <c r="N36" s="26">
@@ -8441,7 +8441,7 @@
       <c r="Q36" s="26">
         <v>5.6922742328772101E-4</v>
       </c>
-      <c r="R36" s="51">
+      <c r="R36" s="48">
         <v>0</v>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
       <c r="L37" s="12">
         <v>3.3677681378858002E-2</v>
       </c>
-      <c r="M37" s="50">
+      <c r="M37" s="47">
         <v>0</v>
       </c>
       <c r="N37" s="28">
@@ -8494,7 +8494,7 @@
       <c r="Q37" s="28">
         <v>3.9591953205020004E-3</v>
       </c>
-      <c r="R37" s="55">
+      <c r="R37" s="52">
         <v>0</v>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       <c r="L38" s="12">
         <v>1.5425291631457999E-2</v>
       </c>
-      <c r="M38" s="50">
+      <c r="M38" s="47">
         <v>0</v>
       </c>
       <c r="N38" s="28">
@@ -8545,7 +8545,7 @@
       <c r="Q38" s="28">
         <v>1.665275213237E-3</v>
       </c>
-      <c r="R38" s="55">
+      <c r="R38" s="52">
         <v>0</v>
       </c>
     </row>
@@ -8581,7 +8581,7 @@
       <c r="L39" s="12">
         <v>1.0982434226919999E-2</v>
       </c>
-      <c r="M39" s="50">
+      <c r="M39" s="47">
         <v>0</v>
       </c>
       <c r="N39" s="28">
@@ -8596,7 +8596,7 @@
       <c r="Q39" s="28">
         <v>1.164624606695E-3</v>
       </c>
-      <c r="R39" s="55">
+      <c r="R39" s="52">
         <v>0</v>
       </c>
     </row>
@@ -8752,7 +8752,7 @@
       <c r="Q42" s="26">
         <v>1.0646838097907701E-4</v>
       </c>
-      <c r="R42" s="48">
+      <c r="R42" s="45">
         <v>0</v>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       <c r="Q44" s="28">
         <v>3.0719107298528698E-4</v>
       </c>
-      <c r="R44" s="54">
+      <c r="R44" s="51">
         <v>0</v>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       <c r="L45" s="12">
         <v>2.7717917301247301E-4</v>
       </c>
-      <c r="M45" s="52">
+      <c r="M45" s="49">
         <v>0</v>
       </c>
       <c r="N45" s="28">
@@ -8907,7 +8907,7 @@
       <c r="Q45" s="28">
         <v>2.1639429366872301E-4</v>
       </c>
-      <c r="R45" s="54">
+      <c r="R45" s="51">
         <v>0</v>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       <c r="L47" s="7">
         <v>7.19299130020633E-4</v>
       </c>
-      <c r="M47" s="53">
+      <c r="M47" s="50">
         <v>0</v>
       </c>
       <c r="N47" s="26">
@@ -9011,7 +9011,7 @@
       <c r="Q47" s="26">
         <v>5.72549077896478E-4</v>
       </c>
-      <c r="R47" s="48">
+      <c r="R47" s="45">
         <v>0</v>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
       <c r="L48" s="7">
         <v>5.0591529349915999E-4</v>
       </c>
-      <c r="M48" s="53">
+      <c r="M48" s="50">
         <v>0</v>
       </c>
       <c r="N48" s="26">
@@ -9062,7 +9062,7 @@
       <c r="Q48" s="26">
         <v>3.9840769507725398E-4</v>
       </c>
-      <c r="R48" s="48">
+      <c r="R48" s="45">
         <v>0</v>
       </c>
     </row>
@@ -9220,7 +9220,7 @@
       <c r="Q51" s="28">
         <v>4.31227783175061E-4</v>
       </c>
-      <c r="R51" s="54">
+      <c r="R51" s="51">
         <v>0</v>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       <c r="L53" s="7">
         <v>1.5499262694170001E-3</v>
       </c>
-      <c r="M53" s="53">
+      <c r="M53" s="50">
         <v>0</v>
       </c>
       <c r="N53" s="26">
@@ -9323,7 +9323,7 @@
       <c r="Q53" s="26">
         <v>1.2320665537579999E-3</v>
       </c>
-      <c r="R53" s="48">
+      <c r="R53" s="45">
         <v>0</v>
       </c>
     </row>
@@ -9358,7 +9358,7 @@
       <c r="L54" s="7">
         <v>1.0870750404770001E-3</v>
       </c>
-      <c r="M54" s="53">
+      <c r="M54" s="50">
         <v>0</v>
       </c>
       <c r="N54" s="26">
@@ -9373,7 +9373,7 @@
       <c r="Q54" s="26">
         <v>8.6203918614429897E-4</v>
       </c>
-      <c r="R54" s="48">
+      <c r="R54" s="45">
         <v>0</v>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       <c r="L56" s="12">
         <v>2.7258073651480002E-3</v>
       </c>
-      <c r="M56" s="52">
+      <c r="M56" s="49">
         <v>0</v>
       </c>
       <c r="N56" s="28">
@@ -9477,7 +9477,7 @@
       <c r="Q56" s="28">
         <v>2.2237694668799999E-3</v>
       </c>
-      <c r="R56" s="54">
+      <c r="R56" s="51">
         <v>0</v>
       </c>
     </row>
@@ -9513,7 +9513,7 @@
       <c r="L57" s="12">
         <v>1.9151221665460001E-3</v>
       </c>
-      <c r="M57" s="52">
+      <c r="M57" s="49">
         <v>0</v>
       </c>
       <c r="N57" s="28">
@@ -9528,7 +9528,7 @@
       <c r="Q57" s="28">
         <v>1.559328498427E-3</v>
       </c>
-      <c r="R57" s="54">
+      <c r="R57" s="51">
         <v>0</v>
       </c>
     </row>
